--- a/output/roomself_excel/13103.xlsx
+++ b/output/roomself_excel/13103.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>412917</v>
+        <v>101436</v>
       </c>
       <c r="D2" t="n">
-        <v>5720</v>
+        <v>2660</v>
       </c>
       <c r="E2" t="n">
-        <v>1036</v>
+        <v>463</v>
       </c>
       <c r="F2" t="n">
-        <v>736</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>88616</v>
+        <v>486948</v>
       </c>
       <c r="D3" t="n">
-        <v>2532</v>
+        <v>5812</v>
       </c>
       <c r="E3" t="n">
-        <v>705</v>
+        <v>845</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>127290</v>
+        <v>93150</v>
       </c>
       <c r="D4" t="n">
-        <v>3636</v>
+        <v>2460</v>
       </c>
       <c r="E4" t="n">
-        <v>298</v>
+        <v>217</v>
       </c>
       <c r="F4" t="n">
-        <v>261</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32320</v>
+        <v>92805</v>
       </c>
       <c r="D5" t="n">
-        <v>1448</v>
+        <v>2456</v>
       </c>
       <c r="E5" t="n">
-        <v>202</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>686396</v>
+        <v>92805</v>
       </c>
       <c r="D6" t="n">
-        <v>8896</v>
+        <v>2456</v>
       </c>
       <c r="E6" t="n">
-        <v>1616</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84085</v>
+        <v>133170</v>
       </c>
       <c r="D7" t="n">
-        <v>2344</v>
+        <v>2924</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>345</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>31948</v>
+        <v>127290</v>
       </c>
       <c r="D8" t="n">
-        <v>1436</v>
+        <v>3636</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>298</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>261</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>28060</v>
+        <v>31948</v>
       </c>
       <c r="D9" t="n">
-        <v>1408</v>
+        <v>1436</v>
       </c>
       <c r="E9" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>93150</v>
+        <v>98012</v>
       </c>
       <c r="D10" t="n">
-        <v>2460</v>
+        <v>2760</v>
       </c>
       <c r="E10" t="n">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="F10" t="n">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>92805</v>
+        <v>28060</v>
       </c>
       <c r="D11" t="n">
-        <v>2456</v>
+        <v>1408</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>122</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>92805</v>
+        <v>412917</v>
       </c>
       <c r="D12" t="n">
-        <v>2456</v>
+        <v>5720</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>799</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>733</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,64 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>133170</v>
+        <v>88616</v>
       </c>
       <c r="D13" t="n">
-        <v>2924</v>
+        <v>2532</v>
       </c>
       <c r="E13" t="n">
-        <v>345</v>
+        <v>209</v>
       </c>
       <c r="F13" t="n">
         <v>35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>32320</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1448</v>
+      </c>
+      <c r="E14" t="n">
+        <v>202</v>
+      </c>
+      <c r="F14" t="n">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>84085</v>
+      </c>
+      <c r="D15" t="n">
+        <v>2344</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/13103.xlsx
+++ b/output/roomself_excel/13103.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,11 +495,27 @@
       <c r="D2" t="n">
         <v>2660</v>
       </c>
-      <c r="E2" t="n">
-        <v>463</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>272</v>
+        <v>237</v>
+      </c>
+      <c r="G2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>428</v>
+      </c>
+      <c r="J2" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -497,12 +533,20 @@
       <c r="D3" t="n">
         <v>5812</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>845</v>
       </c>
-      <c r="F3" t="n">
-        <v>35</v>
-      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2460</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>217</v>
       </c>
-      <c r="F4" t="n">
-        <v>35</v>
+      <c r="G4" t="n">
+        <v>35</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>270</v>
+      </c>
+      <c r="J4" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -541,12 +601,20 @@
       <c r="D5" t="n">
         <v>2456</v>
       </c>
-      <c r="E5" t="n">
-        <v>0</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="G5" t="n">
+        <v>34</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +631,20 @@
       <c r="D6" t="n">
         <v>2456</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="G6" t="n">
+        <v>34</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>2924</v>
       </c>
-      <c r="E7" t="n">
-        <v>345</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>35</v>
+        <v>323</v>
+      </c>
+      <c r="G7" t="n">
+        <v>35</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>386</v>
+      </c>
+      <c r="J7" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="8">
@@ -607,11 +699,27 @@
       <c r="D8" t="n">
         <v>3636</v>
       </c>
-      <c r="E8" t="n">
-        <v>298</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F8" t="n">
-        <v>261</v>
+        <v>205</v>
+      </c>
+      <c r="G8" t="n">
+        <v>36</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>262</v>
+      </c>
+      <c r="J8" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -629,12 +737,12 @@
       <c r="D9" t="n">
         <v>1436</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>2760</v>
       </c>
-      <c r="E10" t="n">
-        <v>310</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>237</v>
+        <v>202</v>
+      </c>
+      <c r="G10" t="n">
+        <v>35</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>275</v>
+      </c>
+      <c r="J10" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -673,12 +797,20 @@
       <c r="D11" t="n">
         <v>1408</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
         <v>122</v>
       </c>
-      <c r="F11" t="n">
-        <v>35</v>
-      </c>
+      <c r="G11" t="n">
+        <v>35</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,11 +827,27 @@
       <c r="D12" t="n">
         <v>5720</v>
       </c>
-      <c r="E12" t="n">
-        <v>799</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>733</v>
+        <v>1175</v>
+      </c>
+      <c r="G12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>729</v>
+      </c>
+      <c r="J12" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="13">
@@ -717,12 +865,20 @@
       <c r="D13" t="n">
         <v>2532</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>209</v>
       </c>
-      <c r="F13" t="n">
-        <v>35</v>
-      </c>
+      <c r="G13" t="n">
+        <v>35</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +895,20 @@
       <c r="D14" t="n">
         <v>1448</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>202</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>43</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +925,12 @@
       <c r="D15" t="n">
         <v>2344</v>
       </c>
-      <c r="E15" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/13103.xlsx
+++ b/output/roomself_excel/13103.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,46 @@
           <t>ExtWallWidth_2</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -517,6 +557,38 @@
       <c r="J2" t="n">
         <v>35</v>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>35</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>56</v>
+      </c>
+      <c r="R2" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -547,6 +619,38 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>598</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>93</v>
+      </c>
+      <c r="R3" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -585,6 +689,26 @@
       <c r="J4" t="n">
         <v>34</v>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>141</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -615,6 +739,26 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>145</v>
+      </c>
+      <c r="N5" t="n">
+        <v>34</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -645,6 +789,26 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>135</v>
+      </c>
+      <c r="N6" t="n">
+        <v>34</v>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -683,6 +847,38 @@
       <c r="J7" t="n">
         <v>34</v>
       </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>94</v>
+      </c>
+      <c r="N7" t="n">
+        <v>35</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>146</v>
+      </c>
+      <c r="R7" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -719,6 +915,38 @@
         <v>262</v>
       </c>
       <c r="J8" t="n">
+        <v>35</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>103</v>
+      </c>
+      <c r="N8" t="n">
+        <v>36</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>94</v>
+      </c>
+      <c r="R8" t="n">
         <v>35</v>
       </c>
     </row>
@@ -743,6 +971,14 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -781,6 +1017,38 @@
       <c r="J10" t="n">
         <v>35</v>
       </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>51</v>
+      </c>
+      <c r="N10" t="n">
+        <v>35</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>91</v>
+      </c>
+      <c r="R10" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -811,6 +1079,14 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -849,6 +1125,38 @@
       <c r="J12" t="n">
         <v>35</v>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>103</v>
+      </c>
+      <c r="N12" t="n">
+        <v>35</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>294</v>
+      </c>
+      <c r="R12" t="n">
+        <v>35</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -879,6 +1187,14 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -909,6 +1225,26 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>101</v>
+      </c>
+      <c r="N14" t="n">
+        <v>43</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -931,6 +1267,14 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
